--- a/koboforms/KF-05_MH_Screening.xlsx
+++ b/koboforms/KF-05_MH_Screening.xlsx
@@ -1824,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bondhu</t>
+          <t>Bandhu</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Bondhu</t>
+          <t>Bandhu</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3256,380 +3256,6 @@
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>অন্যান্য</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>BND-DIC-02</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Bondhu DIC Bandarban</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>বন্ধু ডিআইসি বান্দরবান</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>BND-DIC-03</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Bondhu DIC Chandpur</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>বন্ধু ডিআইসি চাঁদপুর</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>BND-DIC-05</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Bondhu DIC Dhaka</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>বন্ধু ডিআইসি ঢাকা</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>BND-DIC-04</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Bondhu DIC Noakhali</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>বন্ধু ডিআইসি নোয়াখালী</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>BND-DIC-01</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Bondhu DIC Sunamganj</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>বন্ধু ডিআইসি সুনামগঞ্জ</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-01</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>PHD Brothel 01</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 01</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-02</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>PHD Brothel 02</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 02</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-03</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>PHD Brothel 03</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 03</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-04</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>PHD Brothel 04</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 04</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-05</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>PHD Brothel 05</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 05</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-06</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>PHD Brothel 06</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 06</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-07</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>PHD Brothel 07</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 07</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-08</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>PHD Brothel 08</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-09</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>PHD Brothel 09</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 09</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-10</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>PHD Brothel 10</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>PHD-BROTHEL-11</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>PHD Brothel 11</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>পিএইচডি পল্লী 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>center_code</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>PHD-SRHR-01</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>PHD SRHR Service Centre 01</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>পিএইচডি এসআরএইচআর সেবা কেন্দ্র ০১</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3314,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/koboforms/KF-05_MH_Screening.xlsx
+++ b/koboforms/KF-05_MH_Screening.xlsx
@@ -1824,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2954,306 +2954,658 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>meeting_type</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>day_observance</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Day Observance / Awareness Event</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>মহিলা</t>
+          <t>দিবস পালন / সচেতনতা অনুষ্ঠান</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>fistula_type</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>VVF</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>V.V.F (Vesico-Vaginal)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>পুরুষ</t>
+          <t>ভি.ভি.এফ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>fistula_type</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>RVF</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Transgender</t>
+          <t>R.V.F (Recto-Vaginal)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>তৃতীয় লিঙ্গ</t>
+          <t>আর.ভি.এফ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>fistula_type</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>V.V.F + R.V.F (Combined)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>অন্যান্য</t>
+          <t>ভি.ভি.এফ + আর.ভি.এফ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>fistula_type</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>FSW</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>এফএসডব্লিউ</t>
+          <t>অন্যান্য</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>surgery_performed</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>PWID</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>পিডব্লিউআইডি</t>
+          <t>হ্যাঁ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>surgery_performed</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>এমএসএম</t>
+          <t>না</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>surgery_performed</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>MSW / Kothi</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>এমএসডব্লিউ / কথি</t>
+          <t>অপেক্ষমাণ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>delivery_mode</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Transgender</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>তৃতীয় লিঙ্গ</t>
+          <t>বাড়িতে</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>delivery_mode</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>অন্যান্য</t>
+          <t>প্রতিষ্ঠানে</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>survivor_gender</t>
+          <t>delivery_mode</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>মহিলা</t>
+          <t>অন্যান্য</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>survivor_gender</t>
+          <t>delivery_outcome</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Live Birth</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>পুরুষ</t>
+          <t>জীবিত জন্ম</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>survivor_gender</t>
+          <t>delivery_outcome</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>transgender</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Transgender</t>
+          <t>Still Birth</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>তৃতীয় লিঙ্গ</t>
+          <t>মৃত জন্ম</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>delivery_outcome</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>অজানা</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>yes_no</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>হ্যাঁ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>yes_no</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>না</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>মহিলা</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>পুরুষ</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Transgender</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>তৃতীয় লিঙ্গ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>অন্যান্য</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>FSW</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>এফএসডব্লিউ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>PWID</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>পিডব্লিউআইডি</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>এমএসএম</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>MSW / Kothi</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>এমএসডব্লিউ / কথি</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Transgender</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>তৃতীয় লিঙ্গ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>অন্যান্য</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
           <t>survivor_gender</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>মহিলা</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>survivor_gender</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>পুরুষ</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>survivor_gender</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>transgender</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Transgender</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>তৃতীয় লিঙ্গ</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>survivor_gender</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>অন্যান্য</t>
         </is>

--- a/koboforms/KF-05_MH_Screening.xlsx
+++ b/koboforms/KF-05_MH_Screening.xlsx
@@ -1824,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3262,44 +3262,44 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>হ্যাঁ</t>
+          <t>মহিলা</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>না</t>
+          <t>পুরুষ</t>
         </is>
       </c>
     </row>
@@ -3311,17 +3311,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Transgender</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>মহিলা</t>
+          <t>তৃতীয় লিঙ্গ</t>
         </is>
       </c>
     </row>
@@ -3333,61 +3333,61 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>পুরুষ</t>
+          <t>অন্যান্য</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>target_group</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Transgender</t>
+          <t>FSW</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>তৃতীয় লিঙ্গ</t>
+          <t>এফএসডব্লিউ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>target_group</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>PWID</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>অন্যান্য</t>
+          <t>পিডব্লিউআইডি</t>
         </is>
       </c>
     </row>
@@ -3399,17 +3399,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>FSW</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>এফএসডব্লিউ</t>
+          <t>এমএসএম</t>
         </is>
       </c>
     </row>
@@ -3421,17 +3421,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>PWID</t>
+          <t>MSW / Kothi</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>পিডব্লিউআইডি</t>
+          <t>এমএসডব্লিউ / কথি</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>Transgender</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>এমএসএম</t>
+          <t>তৃতীয় লিঙ্গ</t>
         </is>
       </c>
     </row>
@@ -3465,61 +3465,61 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>MSW / Kothi</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>এমএসডব্লিউ / কথি</t>
+          <t>অন্যান্য</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>survivor_gender</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Transgender</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>তৃতীয় লিঙ্গ</t>
+          <t>মহিলা</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>target_group</t>
+          <t>survivor_gender</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>অন্যান্য</t>
+          <t>পুরুষ</t>
         </is>
       </c>
     </row>
@@ -3531,17 +3531,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>transgender</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Transgender</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>মহিলা</t>
+          <t>তৃতীয় লিঙ্গ</t>
         </is>
       </c>
     </row>
@@ -3553,59 +3553,15 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>পুরুষ</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>survivor_gender</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>transgender</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Transgender</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>তৃতীয় লিঙ্গ</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>survivor_gender</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>অন্যান্য</t>
         </is>

--- a/koboforms/KF-05_MH_Screening.xlsx
+++ b/koboforms/KF-05_MH_Screening.xlsx
@@ -1824,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3564,6 +3564,28 @@
       <c r="D83" s="3" t="inlineStr">
         <is>
           <t>অন্যান্য</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>center_code</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Placeholder — seed ServiceCenters before deployment</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>প্লেসহোল্ডার — প্রকৃত কেন্দ্র যোগ করুন</t>
         </is>
       </c>
     </row>
